--- a/data/trans_dic/P25C$productsfarma_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Habitat-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 10,07</t>
+          <t>0,0; 9,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 2,28</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 6,62</t>
+          <t>0,0; 7,11</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,66</t>
+          <t>0,0; 3,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 11,49</t>
+          <t>1,57; 12,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,18; 4,03</t>
+          <t>0,26; 4,23</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 7,44</t>
+          <t>1,21; 7,62</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,22; 5,85</t>
+          <t>0,41; 6,92</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,2; 5,47</t>
+          <t>1,16; 5,24</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,1; 11,06</t>
+          <t>3,46; 11,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,91; 7,21</t>
+          <t>1,99; 7,23</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,31; 8,2</t>
+          <t>3,08; 8,2</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,99; 4,73</t>
+          <t>0,97; 4,49</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,73; 5,38</t>
+          <t>1,81; 5,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,32; 4,16</t>
+          <t>1,45; 4,16</t>
         </is>
       </c>
     </row>
@@ -825,7 +825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos</t>
+          <t>Población cuyo método para dejar de fumar fue, por su cuenta, con parches, chicles u otros productos farmaceuticos (tasa de respuesta: 99,69%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -930,17 +930,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 11526</t>
+          <t>0; 11427</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 1122</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 10838</t>
+          <t>0; 11638</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 14603</t>
+          <t>0; 14955</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1312; 9579</t>
+          <t>1312; 10428</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>845; 19426</t>
+          <t>1247; 20424</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1641; 10523</t>
+          <t>1707; 10775</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>165; 4380</t>
+          <t>304; 5183</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2598; 11827</t>
+          <t>2515; 11341</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6029; 21526</t>
+          <t>6730; 21646</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2482; 9374</t>
+          <t>2588; 9399</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10754; 26644</t>
+          <t>10008; 26617</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8387; 40205</t>
+          <t>8218; 38177</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>5844; 18144</t>
+          <t>6096; 16891</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>15660; 49324</t>
+          <t>17238; 49429</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P25C$productsfarma_2023-Habitat-trans_dic.xlsx
+++ b/data/trans_dic/P25C$productsfarma_2023-Habitat-trans_dic.xlsx
@@ -549,7 +549,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -559,7 +559,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -572,7 +572,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 9,98</t>
+          <t>0,0; 10,33</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -582,7 +582,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 7,11</t>
+          <t>0,0; 7,54</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,18%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>3,09%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 3,75</t>
+          <t>0,72; 6,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>1,57; 12,51</t>
+          <t>1,51; 10,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0,26; 4,23</t>
+          <t>1,38; 5,75</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,48%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,73%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,21; 7,62</t>
+          <t>1,03; 6,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,41; 6,92</t>
+          <t>0,77; 6,56</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1,16; 5,24</t>
+          <t>1,17; 5,32</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>3,46; 11,12</t>
+          <t>3,21; 10,82</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1,99; 7,23</t>
+          <t>2,09; 7,37</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3,08; 8,2</t>
+          <t>3,24; 8,36</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,5%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>0,97; 4,49</t>
+          <t>2,33; 5,59</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 5,01</t>
+          <t>1,76; 5,0</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1,45; 4,16</t>
+          <t>2,49; 4,97</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3493</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -917,7 +917,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3153</t>
+          <t>3493</t>
         </is>
       </c>
     </row>
@@ -930,7 +930,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 11427</t>
+          <t>0; 12694</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -940,7 +940,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>0; 11638</t>
+          <t>0; 13250</t>
         </is>
       </c>
     </row>
@@ -980,17 +980,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>4305</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3638</t>
+          <t>3765</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>7839</t>
+          <t>8071</t>
         </is>
       </c>
     </row>
@@ -1003,17 +1003,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 14955</t>
+          <t>1235; 11360</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1312; 10428</t>
+          <t>1364; 9791</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1247; 20424</t>
+          <t>3599; 15021</t>
         </is>
       </c>
     </row>
@@ -1053,17 +1053,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>4548</t>
+          <t>4700</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>1436</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5984</t>
+          <t>6774</t>
         </is>
       </c>
     </row>
@@ -1076,17 +1076,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>1707; 10775</t>
+          <t>1699; 10230</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>304; 5183</t>
+          <t>643; 5481</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2515; 11341</t>
+          <t>2914; 13192</t>
         </is>
       </c>
     </row>
@@ -1126,17 +1126,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>11592</t>
+          <t>11932</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>5248</t>
+          <t>5659</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>16840</t>
+          <t>17591</t>
         </is>
       </c>
     </row>
@@ -1149,17 +1149,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>6730; 21646</t>
+          <t>6475; 21835</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>2588; 9399</t>
+          <t>2914; 10274</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10008; 26617</t>
+          <t>11039; 28513</t>
         </is>
       </c>
     </row>
@@ -1199,17 +1199,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>23495</t>
+          <t>24430</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10322</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>33817</t>
+          <t>35928</t>
         </is>
       </c>
     </row>
@@ -1222,17 +1222,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>8218; 38177</t>
+          <t>15407; 36890</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>6096; 16891</t>
+          <t>6448; 18308</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>17238; 49429</t>
+          <t>25587; 50963</t>
         </is>
       </c>
     </row>
